--- a/forms/trg/Formulir_TRG_empogo.xlsx
+++ b/forms/trg/Formulir_TRG_empogo.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B25)</f>
+        <f>COUNTA(Anggota!B5:B26)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F25)</f>
+        <f>COUNTA(Anggota!F5:F26)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,22 +925,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Chaeroel Ansar, S.IP., M.Sc</t>
+          <t>Prof. Dr. Andi M. Rusli, M.Si</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Department of Government Science, Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Comparative Government</t>
+          <t>Governmental Ecology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -949,17 +945,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0646-8141</t>
+          <t>0000-0002-9342-3840</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6876315</t>
+          <t>6025565</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>58995851200</t>
+          <t>57210430463</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -974,12 +970,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. A. Lukman Irwan, M.Si</t>
+          <t>Muhammad Chaeroel Ansar, S.IP., M.Sc</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -989,7 +985,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Bureaucracy Reform</t>
+          <t>Comparative Government</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -998,17 +994,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0009-0003-8943-2626</t>
+          <t>0000-0003-0646-8141</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6723289</t>
+          <t>6876315</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57215047052</t>
+          <t>58995851200</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1023,12 +1019,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Suhardiman Syamsu, M.Si</t>
+          <t>Dr. A. Lukman Irwan, M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1038,7 +1034,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Governance and Local Studies</t>
+          <t>Bureaucracy Reform</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1047,17 +1043,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0009-0000-5955-4110</t>
+          <t>0009-0003-8943-2626</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6751204</t>
+          <t>6723289</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>59219073900</t>
+          <t>57215047052</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1072,22 +1068,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Takuji W. Tsusaka, Ph.D</t>
+          <t>Dr. Suhardiman Syamsu, M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Department of Food, Agriculture, and Natural Resources, Asian Institute of Technology, Thailand</t>
+          <t>Department of Government Science, Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Social Capital Formation</t>
+          <t>Governance and Local Studies</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1096,13 +1092,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-9872-2436</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="n"/>
+          <t>0009-0000-5955-4110</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>6751204</t>
+        </is>
+      </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>56659390600</t>
+          <t>59219073900</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1117,22 +1117,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Siran Liang</t>
+          <t>Takuji W. Tsusaka, Ph.D</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Institute of Geosystems and Bioindications, TU Braunschweig, Germany</t>
+          <t>Department of Food, Agriculture, and Natural Resources, Asian Institute of Technology, Thailand</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Environmental Anthropology and Political Ecology</t>
+          <t>Social Capital Formation</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1141,13 +1141,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1265-6029</t>
+          <t>0000-0002-9872-2436</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57205289279</t>
+          <t>56659390600</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1162,22 +1162,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Yusriah Amaliah, S.IP., M.AP</t>
+          <t>Siran Liang</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Department of Government Science, Hasanuddin University</t>
+          <t>Institute of Geosystems and Bioindications, TU Braunschweig, Germany</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Public Policy and Gender</t>
+          <t>Environmental Anthropology and Political Ecology</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1186,17 +1186,13 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0009-0004-0640-576X</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>6819463</t>
-        </is>
-      </c>
+          <t>0000-0002-1265-6029</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>59120519000</t>
+          <t>57205289279</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1211,12 +1207,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>A. Hasyim Asyari, S.IP., M.Si</t>
+          <t>Yusriah Amaliah, S.IP., M.AP</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1226,18 +1222,26 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Data Science and Environmental Informatics</t>
+          <t>Public Policy and Gender</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0009-0004-0640-576X</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6819463</t>
+        </is>
+      </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>59506102900</t>
+          <t>59120519000</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1252,12 +1256,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Irwan Ade Saputra, S.IP., M.Si</t>
+          <t>A. Hasyim Asyari, S.IP., M.Si</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1267,7 +1271,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Government Bureaucracy</t>
+          <t>Data Science and Environmental Informatics</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1275,14 +1279,10 @@
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>6874805</t>
-        </is>
-      </c>
+      <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>58651442300</t>
+          <t>59506102900</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Andi Nurhadi, S.IP</t>
+          <t>Dr. Irwan Ade Saputra, S.IP., M.Si</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Master Student</t>
+          <t>Government Bureaucracy</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1320,8 +1320,16 @@
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>6874805</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>58651442300</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1332,10 +1340,26 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="11" t="n"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Andi Nurhadi, S.IP</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Department of Government Science, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Master Student</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1343,7 +1367,11 @@
       <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1532,15 +1560,32 @@
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="12" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
